--- a/out/Attention-mamba2_repeat_4_000007.xlsx
+++ b/out/Attention-mamba2_repeat_4_000007.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.905315212968727</v>
+        <v>7.399999562500023</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.905315212968727</v>
+        <v>0.04545455991735464</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.9209439647931166</v>
+        <v>7.999999562500022</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.520943964793117</v>
+        <v>0.04545455991735464</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.520943964793117</v>
+        <v>0.04545455991735464</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.305315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.305315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001702294543631142</v>
+        <v>-5.77114113640273e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.962494120363665</v>
+        <v>0.6653272630790739</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC40" t="n">
-        <v>3.928022054024003</v>
+        <v>1.331683153591536</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.2942847475944523</v>
+        <v>0.09976881366469541</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC41" t="n">
-        <v>2.551463385705258</v>
+        <v>0.8650004056209782</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.3679516885574564</v>
+        <v>0.1247434230127987</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC42" t="n">
-        <v>2.993128817898847</v>
+        <v>1.014734395541674</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.5274571632473367</v>
+        <v>0.1788191053054309</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC43" t="n">
-        <v>3.680298993842492</v>
+        <v>1.2476997935614</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.5642746860731285</v>
+        <v>0.1913013702867537</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC44" t="n">
-        <v>4.281430528999383</v>
+        <v>1.451496435934952</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5980174324069149</v>
+        <v>0.2027401561802915</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC45" t="n">
-        <v>4.913233406399749</v>
+        <v>1.66569133039293</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.2698741448537649</v>
+        <v>0.09149352762836521</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC46" t="n">
-        <v>4.854467313589955</v>
+        <v>1.645768276485645</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1303368769506152</v>
+        <v>0.04418654882931739</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC47" t="n">
-        <v>4.845055304431301</v>
+        <v>1.642577390389271</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.06210102859558056</v>
+        <v>0.02105418789541849</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC48" t="n">
-        <v>4.838818205843535</v>
+        <v>1.640462839758584</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.0184001015891539</v>
+        <v>0.006235117151465533</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC49" t="n">
-        <v>4.813450730942816</v>
+        <v>1.631859551337151</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01217016840179297</v>
+        <v>0.004122599330277831</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC50" t="n">
-        <v>4.819381925069963</v>
+        <v>1.633867027066029</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.006226387758716111</v>
+        <v>0.002107551637133032</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC51" t="n">
-        <v>4.819657291212861</v>
+        <v>1.633957076191057</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.003182092327199138</v>
+        <v>0.001075148473494844</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC52" t="n">
-        <v>4.819792388511122</v>
+        <v>1.633999572079852</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001193148823900667</v>
+        <v>0.0004014472005272636</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC53" t="n">
-        <v>4.818993929191969</v>
+        <v>1.63372549225492</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0006484047339888131</v>
+        <v>0.0002161016019053054</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC54" t="n">
-        <v>4.81909616507425</v>
+        <v>1.633756847347282</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.000309713060421098</v>
+        <v>0.000101493813374816</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC55" t="n">
-        <v>4.819066773298172</v>
+        <v>1.633743563252066</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.000189823113252138</v>
+        <v>6.092499286814771e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC56" t="n">
-        <v>4.819136559301159</v>
+        <v>1.633764059079324</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>9.690754659105971e-05</v>
+        <v>2.999855135450535e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC57" t="n">
-        <v>4.819140438087294</v>
+        <v>1.633762108359411</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>4.395556340847371e-05</v>
+        <v>1.198458322334802e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.305315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC58" t="n">
-        <v>4.819132377569588</v>
+        <v>1.633756057063693</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>2.697865944406779e-05</v>
+        <v>5.233171022101693e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.305315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC59" t="n">
-        <v>4.819141358240592</v>
+        <v>1.633755811268129</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>8.987335331640211e-06</v>
+        <v>-3.375548894532629e-07</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC60" t="n">
-        <v>4.819133499458745</v>
+        <v>1.633749782559842</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>1.176214944912711e-06</v>
+        <v>-2.941261685029097e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC61" t="n">
-        <v>4.819126718668275</v>
+        <v>1.633744098025814</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-1.662115307266386e-06</v>
+        <v>-3.887371769088796e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC62" t="n">
-        <v>4.819122298124424</v>
+        <v>1.6337393467506</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-3.062365791830193e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC63" t="n">
-        <v>4.8191167198293</v>
+        <v>1.633734057603038</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.053889915940302e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC64" t="n">
-        <v>4.819111673208233</v>
+        <v>1.633734034868737</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC65" t="n">
-        <v>4.819111991488449</v>
+        <v>1.633734353148953</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC66" t="n">
-        <v>4.819113082734906</v>
+        <v>1.633735444395411</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.305315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC67" t="n">
-        <v>4.81911239312777</v>
+        <v>1.633734754788275</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.305315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC68" t="n">
-        <v>4.819112423440172</v>
+        <v>1.633734785100676</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC69" t="n">
-        <v>4.819112233987662</v>
+        <v>1.633734595648166</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC70" t="n">
-        <v>4.819112287034366</v>
+        <v>1.633734648694869</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC71" t="n">
-        <v>4.819112340081068</v>
+        <v>1.633734701741572</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.520943964793117</v>
+        <v>7.999999562500022</v>
       </c>
       <c r="JC72" t="n">
-        <v>4.819112302190566</v>
+        <v>1.63373466385107</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.305315212968727</v>
+        <v>7.999999562500022</v>
       </c>
       <c r="JC73" t="n">
-        <v>4.819112173362859</v>
+        <v>1.633734535023363</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.305315212968727</v>
+        <v>0.04545455991735464</v>
       </c>
       <c r="JC74" t="n">
-        <v>4.819112029378951</v>
+        <v>1.633734391039456</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.905315212968727</v>
+        <v>0.04545455991735464</v>
       </c>
       <c r="JC75" t="n">
-        <v>4.819111870238843</v>
+        <v>1.633734231899347</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC76" t="n">
-        <v>4.819111923285546</v>
+        <v>1.63373428494605</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC77" t="n">
-        <v>4.819111870238843</v>
+        <v>1.633734231899347</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.305315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC78" t="n">
-        <v>4.819111870238843</v>
+        <v>1.633734231899347</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.305315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC79" t="n">
-        <v>4.819111688364434</v>
+        <v>1.633734050024938</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC80" t="n">
-        <v>4.819111855082642</v>
+        <v>1.633734216743147</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC81" t="n">
-        <v>4.819112052113253</v>
+        <v>1.633734413773757</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC82" t="n">
-        <v>4.819111892973145</v>
+        <v>1.633734254633649</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.305315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC83" t="n">
-        <v>4.819111930863646</v>
+        <v>1.63373429252415</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC84" t="n">
-        <v>4.819112127894257</v>
+        <v>1.633734489554761</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC85" t="n">
-        <v>4.819112105159955</v>
+        <v>1.63373446682046</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC86" t="n">
-        <v>4.819111953597947</v>
+        <v>1.633734315258452</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC87" t="n">
-        <v>4.819111877816943</v>
+        <v>1.633734239477448</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.305315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC88" t="n">
-        <v>4.819111976332249</v>
+        <v>1.633734337992753</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC89" t="n">
-        <v>4.819111983910349</v>
+        <v>1.633734345570854</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC90" t="n">
-        <v>4.819112249143863</v>
+        <v>1.633734610804367</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC91" t="n">
-        <v>4.819111953597947</v>
+        <v>1.633734315258452</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC92" t="n">
-        <v>4.819112196097159</v>
+        <v>1.633734557757665</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC93" t="n">
-        <v>4.819112279456264</v>
+        <v>1.633734641116769</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC94" t="n">
-        <v>4.819112112738056</v>
+        <v>1.63373447439856</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.305315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC95" t="n">
-        <v>4.819112302190566</v>
+        <v>1.63373466385107</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.305315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC96" t="n">
-        <v>4.819111953597947</v>
+        <v>1.633734315258452</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC97" t="n">
-        <v>4.819111748989236</v>
+        <v>1.633734110649741</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC98" t="n">
-        <v>4.819111862660742</v>
+        <v>1.633734224321247</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.305315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC99" t="n">
-        <v>4.819111877816943</v>
+        <v>1.633734239477448</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC100" t="n">
-        <v>4.819111642895832</v>
+        <v>1.633734004556336</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC101" t="n">
-        <v>4.819111703520634</v>
+        <v>1.633734065181139</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC102" t="n">
-        <v>4.819111574692927</v>
+        <v>1.633733936353432</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.305315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC103" t="n">
-        <v>4.819111711098735</v>
+        <v>1.633734072759239</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC104" t="n">
-        <v>4.819111885395044</v>
+        <v>1.633734247055548</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC105" t="n">
-        <v>4.819112029378951</v>
+        <v>1.633734391039456</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC106" t="n">
-        <v>4.819111862660742</v>
+        <v>1.633734224321247</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC107" t="n">
-        <v>4.819111855082642</v>
+        <v>1.633734216743147</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC108" t="n">
-        <v>4.819111567114827</v>
+        <v>1.633733928775331</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC109" t="n">
-        <v>4.819111582271028</v>
+        <v>1.633733943931533</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC110" t="n">
-        <v>4.81911180961404</v>
+        <v>1.633734171274544</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC111" t="n">
-        <v>4.819111794457839</v>
+        <v>1.633734156118344</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC112" t="n">
-        <v>4.819111900551245</v>
+        <v>1.633734262211749</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC113" t="n">
-        <v>4.81911162773963</v>
+        <v>1.633733989400135</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC114" t="n">
-        <v>4.819111726254936</v>
+        <v>1.63373408791544</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC115" t="n">
-        <v>4.819111877816943</v>
+        <v>1.633734239477448</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC116" t="n">
-        <v>4.819111892973145</v>
+        <v>1.633734254633649</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC117" t="n">
-        <v>4.819111870238843</v>
+        <v>1.633734231899347</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC118" t="n">
-        <v>4.819111953597947</v>
+        <v>1.633734315258452</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC119" t="n">
-        <v>4.819112052113253</v>
+        <v>1.633734413773757</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC120" t="n">
-        <v>4.819111885395044</v>
+        <v>1.633734247055548</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC121" t="n">
-        <v>4.819111870238843</v>
+        <v>1.633734231899347</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC122" t="n">
-        <v>4.819111839926441</v>
+        <v>1.633734201586946</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC123" t="n">
-        <v>4.819111824770241</v>
+        <v>1.633734186430745</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC124" t="n">
-        <v>4.819111862660742</v>
+        <v>1.633734224321247</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC125" t="n">
-        <v>4.819111877816943</v>
+        <v>1.633734239477448</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.9209439647931166</v>
+        <v>-0.5545454400826453</v>
       </c>
       <c r="JC126" t="n">
-        <v>4.819111870238843</v>
+        <v>1.633734231899347</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_4_000007.xlsx
+++ b/out/Attention-mamba2_repeat_4_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.905315212968727</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.905315212968727</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.4947854768329916</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.1512166209411443</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.520943964793117</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.520943964793117</v>
+        <v>0.3512166209411443</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.305315212968727</v>
+        <v>0.3512166209411444</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.4947854768329915</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.905315212968727</v>
+        <v>0.1512166209411443</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.4947854768329915</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.4947854768329915</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.4947854768329915</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.1512166209411443</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.520943964793117</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.520943964793117</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.520943964793117</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.520943964793117</v>
+        <v>0.3512166209411443</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.305315212968727</v>
+        <v>0.3512166209411444</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.1512166209411443</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.520943964793117</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.520943964793117</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.520943964793117</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.520943964793117</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.520943964793117</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.520943964793117</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.520943964793117</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001702294543631142</v>
+        <v>-0.0001607944000447169</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.962494120363665</v>
+        <v>1.853721954411314</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC40" t="n">
-        <v>3.928022054024003</v>
+        <v>3.710309428425272</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.2942847475944523</v>
+        <v>0.2779738761016717</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.1512166209411443</v>
       </c>
       <c r="JC41" t="n">
-        <v>2.551463385705258</v>
+        <v>2.410047276375039</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.3679516885574564</v>
+        <v>0.3475577352364625</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.905315212968727</v>
+        <v>0.1512166209411443</v>
       </c>
       <c r="JC42" t="n">
-        <v>2.993128817898847</v>
+        <v>2.827233128512782</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.5274571632473367</v>
+        <v>0.49822252787801</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.1512166209411443</v>
       </c>
       <c r="JC43" t="n">
-        <v>3.680298993842492</v>
+        <v>3.476316477828255</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.5642746860731285</v>
+        <v>0.5329994170182389</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.1512166209411443</v>
       </c>
       <c r="JC44" t="n">
-        <v>4.281430528999383</v>
+        <v>4.044129930562831</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5980174324069149</v>
+        <v>0.5648719510311713</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.4947854768329915</v>
       </c>
       <c r="JC45" t="n">
-        <v>4.913233406399749</v>
+        <v>4.640914747667312</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.2698741448537649</v>
+        <v>0.2549162055742312</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.905315212968727</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC46" t="n">
-        <v>4.854467313589955</v>
+        <v>4.585405801437531</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1303368769506152</v>
+        <v>0.1231128759542703</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.905315212968727</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC47" t="n">
-        <v>4.845055304431301</v>
+        <v>4.576515458634022</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.06210102859558056</v>
+        <v>0.05865900719302262</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.905315212968727</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC48" t="n">
-        <v>4.838818205843535</v>
+        <v>4.570624055095799</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.0184001015891539</v>
+        <v>0.01738025465728496</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.905315212968727</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC49" t="n">
-        <v>4.813450730942816</v>
+        <v>4.54666257413703</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01217016840179297</v>
+        <v>0.01149537223741126</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.905315212968727</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC50" t="n">
-        <v>4.819381925069963</v>
+        <v>4.552264760820843</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.006226387758716111</v>
+        <v>0.005881019512496411</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.905315212968727</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC51" t="n">
-        <v>4.819657291212861</v>
+        <v>4.552524587959138</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.003182092327199138</v>
+        <v>0.003005926453143595</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.905315212968727</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC52" t="n">
-        <v>4.819792388511122</v>
+        <v>4.552651919930332</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001193148823900667</v>
+        <v>0.001126542951188564</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.905315212968727</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC53" t="n">
-        <v>4.818993929191969</v>
+        <v>4.551897555629047</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0006484047339888131</v>
+        <v>0.0006121044709894347</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.905315212968727</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC54" t="n">
-        <v>4.81909616507425</v>
+        <v>4.551993833962312</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.000309713060421098</v>
+        <v>0.0002922290015088148</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.905315212968727</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC55" t="n">
-        <v>4.819066773298172</v>
+        <v>4.551965797284904</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.000189823113252138</v>
+        <v>0.0001789996069603525</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.2947854768329915</v>
       </c>
       <c r="JC56" t="n">
-        <v>4.819136559301159</v>
+        <v>4.552031428509947</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>9.690754659105971e-05</v>
+        <v>9.073133164614701e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.2947854768329914</v>
       </c>
       <c r="JC57" t="n">
-        <v>4.819140438087294</v>
+        <v>4.552034814656435</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>4.395556340847371e-05</v>
+        <v>4.195737714690335e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.305315212968727</v>
+        <v>-0.2947854768329914</v>
       </c>
       <c r="JC58" t="n">
-        <v>4.819132377569588</v>
+        <v>4.552026908132978</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>2.697865944406779e-05</v>
+        <v>2.442036668854237e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.305315212968727</v>
+        <v>-0.9407875746071271</v>
       </c>
       <c r="JC59" t="n">
-        <v>4.819141358240592</v>
+        <v>4.552035050740018</v>
       </c>
     </row>
     <row r="60">
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.9407875746071271</v>
       </c>
       <c r="JC60" t="n">
-        <v>4.819133499458745</v>
+        <v>4.552027305629676</v>
       </c>
     </row>
     <row r="61">
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.905315212968727</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC61" t="n">
-        <v>4.819126718668275</v>
+        <v>4.552020661245013</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.905315212968727</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC62" t="n">
-        <v>4.819122298124424</v>
+        <v>4.552016157342058</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-3.062365791830193e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.905315212968727</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC63" t="n">
-        <v>4.8191167198293</v>
+        <v>4.552010724210589</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.905315212968727</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC64" t="n">
-        <v>4.819111673208233</v>
+        <v>4.552005677589522</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.4947854768329913</v>
       </c>
       <c r="JC65" t="n">
-        <v>4.819111991488449</v>
+        <v>4.552005995869738</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.2947854768329914</v>
       </c>
       <c r="JC66" t="n">
-        <v>4.819113082734906</v>
+        <v>4.552007087116195</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.305315212968727</v>
+        <v>-0.2947854768329914</v>
       </c>
       <c r="JC67" t="n">
-        <v>4.81911239312777</v>
+        <v>4.552006397509059</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.305315212968727</v>
+        <v>-0.9407875746071271</v>
       </c>
       <c r="JC68" t="n">
-        <v>4.819112423440172</v>
+        <v>4.552006427821461</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.9407875746071271</v>
       </c>
       <c r="JC69" t="n">
-        <v>4.819112233987662</v>
+        <v>4.552006238368951</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.905315212968727</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC70" t="n">
-        <v>4.819112287034366</v>
+        <v>4.552006291415654</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.4947854768329915</v>
       </c>
       <c r="JC71" t="n">
-        <v>4.819112340081068</v>
+        <v>4.552006344462357</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.2947854768329913</v>
       </c>
       <c r="JC72" t="n">
-        <v>4.819112302190566</v>
+        <v>4.552006306571855</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.305315212968727</v>
+        <v>-0.2947854768329913</v>
       </c>
       <c r="JC73" t="n">
-        <v>4.819112173362859</v>
+        <v>4.552006177744147</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.305315212968727</v>
+        <v>-0.9407875746071271</v>
       </c>
       <c r="JC74" t="n">
-        <v>4.819112029378951</v>
+        <v>4.55200603376024</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.2947854768329914</v>
       </c>
       <c r="JC75" t="n">
-        <v>4.819111870238843</v>
+        <v>4.552005874620132</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.520943964793117</v>
+        <v>0.3512166209411444</v>
       </c>
       <c r="JC76" t="n">
-        <v>4.819111923285546</v>
+        <v>4.552005927666834</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.520943964793117</v>
+        <v>0.3512166209411444</v>
       </c>
       <c r="JC77" t="n">
-        <v>4.819111870238843</v>
+        <v>4.552005874620132</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.305315212968727</v>
+        <v>-0.2947854768329914</v>
       </c>
       <c r="JC78" t="n">
-        <v>4.819111870238843</v>
+        <v>4.552005874620132</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.305315212968727</v>
+        <v>-0.9407875746071271</v>
       </c>
       <c r="JC79" t="n">
-        <v>4.819111688364434</v>
+        <v>4.552005692745722</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.4947854768329913</v>
       </c>
       <c r="JC80" t="n">
-        <v>4.819111855082642</v>
+        <v>4.552005859463931</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.1512166209411444</v>
       </c>
       <c r="JC81" t="n">
-        <v>4.819112052113253</v>
+        <v>4.552006056494541</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.520943964793117</v>
+        <v>0.3512166209411445</v>
       </c>
       <c r="JC82" t="n">
-        <v>4.819111892973145</v>
+        <v>4.552005897354434</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.305315212968727</v>
+        <v>-0.2947854768329913</v>
       </c>
       <c r="JC83" t="n">
-        <v>4.819111930863646</v>
+        <v>4.552005935244934</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.905315212968727</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC84" t="n">
-        <v>4.819112127894257</v>
+        <v>4.552006132275545</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.4947854768329913</v>
       </c>
       <c r="JC85" t="n">
-        <v>4.819112105159955</v>
+        <v>4.552006109541244</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.1512166209411444</v>
       </c>
       <c r="JC86" t="n">
-        <v>4.819111953597947</v>
+        <v>4.552005957979236</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.520943964793117</v>
+        <v>0.3512166209411445</v>
       </c>
       <c r="JC87" t="n">
-        <v>4.819111877816943</v>
+        <v>4.552005882198232</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.305315212968727</v>
+        <v>-0.2947854768329913</v>
       </c>
       <c r="JC88" t="n">
-        <v>4.819111976332249</v>
+        <v>4.552005980713538</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.905315212968727</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC89" t="n">
-        <v>4.819111983910349</v>
+        <v>4.552005988291638</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.905315212968727</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC90" t="n">
-        <v>4.819112249143863</v>
+        <v>4.552006253525152</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.905315212968727</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC91" t="n">
-        <v>4.819111953597947</v>
+        <v>4.552005957979236</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.905315212968727</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC92" t="n">
-        <v>4.819112196097159</v>
+        <v>4.552006200478449</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.905315212968727</v>
+        <v>-0.4947854768329915</v>
       </c>
       <c r="JC93" t="n">
-        <v>4.819112279456264</v>
+        <v>4.552006283837553</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.520943964793117</v>
+        <v>-0.4947854768329913</v>
       </c>
       <c r="JC94" t="n">
-        <v>4.819112112738056</v>
+        <v>4.552006117119345</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.305315212968727</v>
+        <v>-0.2947854768329913</v>
       </c>
       <c r="JC95" t="n">
-        <v>4.819112302190566</v>
+        <v>4.552006306571855</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.305315212968727</v>
+        <v>-0.2947854768329913</v>
       </c>
       <c r="JC96" t="n">
-        <v>4.819111953597947</v>
+        <v>4.552005957979236</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.520943964793117</v>
+        <v>0.3512166209411445</v>
       </c>
       <c r="JC97" t="n">
-        <v>4.819111748989236</v>
+        <v>4.552005753370525</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.520943964793117</v>
+        <v>0.3512166209411445</v>
       </c>
       <c r="JC98" t="n">
-        <v>4.819111862660742</v>
+        <v>4.552005867042031</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.305315212968727</v>
+        <v>0.3512166209411445</v>
       </c>
       <c r="JC99" t="n">
-        <v>4.819111877816943</v>
+        <v>4.552005882198232</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.520943964793117</v>
+        <v>0.3512166209411445</v>
       </c>
       <c r="JC100" t="n">
-        <v>4.819111642895832</v>
+        <v>4.55200564727712</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.520943964793117</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC101" t="n">
-        <v>4.819111703520634</v>
+        <v>4.552005707901923</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.520943964793117</v>
+        <v>0.3512166209411445</v>
       </c>
       <c r="JC102" t="n">
-        <v>4.819111574692927</v>
+        <v>4.552005579074216</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.305315212968727</v>
+        <v>0.3512166209411445</v>
       </c>
       <c r="JC103" t="n">
-        <v>4.819111711098735</v>
+        <v>4.552005715480024</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.520943964793117</v>
+        <v>0.3512166209411445</v>
       </c>
       <c r="JC104" t="n">
-        <v>4.819111885395044</v>
+        <v>4.552005889776332</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.1512166209411445</v>
       </c>
       <c r="JC105" t="n">
-        <v>4.819112029378951</v>
+        <v>4.55200603376024</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.905315212968727</v>
+        <v>0.1512166209411444</v>
       </c>
       <c r="JC106" t="n">
-        <v>4.819111862660742</v>
+        <v>4.552005867042031</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.1512166209411444</v>
       </c>
       <c r="JC107" t="n">
-        <v>4.819111855082642</v>
+        <v>4.552005859463931</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC108" t="n">
-        <v>4.819111567114827</v>
+        <v>4.552005571496116</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.520943964793117</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC109" t="n">
-        <v>4.819111582271028</v>
+        <v>4.552005586652317</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.520943964793117</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC110" t="n">
-        <v>4.81911180961404</v>
+        <v>4.552005813995328</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.520943964793117</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC111" t="n">
-        <v>4.819111794457839</v>
+        <v>4.552005798839128</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.520943964793117</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC112" t="n">
-        <v>4.819111900551245</v>
+        <v>4.552005904932534</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.520943964793117</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC113" t="n">
-        <v>4.81911162773963</v>
+        <v>4.552005632120919</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.520943964793117</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC114" t="n">
-        <v>4.819111726254936</v>
+        <v>4.552005730636224</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.520943964793117</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC115" t="n">
-        <v>4.819111877816943</v>
+        <v>4.552005882198232</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC116" t="n">
-        <v>4.819111892973145</v>
+        <v>4.552005897354434</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC117" t="n">
-        <v>4.819111870238843</v>
+        <v>4.552005874620132</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC118" t="n">
-        <v>4.819111953597947</v>
+        <v>4.552005957979236</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC119" t="n">
-        <v>4.819112052113253</v>
+        <v>4.552006056494541</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC120" t="n">
-        <v>4.819111885395044</v>
+        <v>4.552005889776332</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC121" t="n">
-        <v>4.819111870238843</v>
+        <v>4.552005874620132</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC122" t="n">
-        <v>4.819111839926441</v>
+        <v>4.55200584430773</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC123" t="n">
-        <v>4.819111824770241</v>
+        <v>4.55200582915153</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC124" t="n">
-        <v>4.819111862660742</v>
+        <v>4.552005867042031</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC125" t="n">
-        <v>4.819111877816943</v>
+        <v>4.552005882198232</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.9209439647931166</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC126" t="n">
-        <v>4.819111870238843</v>
+        <v>4.552005874620132</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_4_000007.xlsx
+++ b/out/Attention-mamba2_repeat_4_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.07961051166057587</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.140787574607127</v>
+        <v>-1.28</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.04634322226047516</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.8599999999999997</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.02621113881468773</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.4947854768329916</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.04897912219166756</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.1512166209411443</v>
+        <v>-0.16</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.01812337711453438</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.003646623343229294</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.3512166209411443</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.004249747842550278</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.3512166209411444</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.003217112272977829</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.4947854768329915</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.0004043895751237869</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.1512166209411443</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.002018257975578308</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.4947854768329915</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.0004030074924230576</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.4947854768329915</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.0008475035429000854</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.4947854768329915</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.002036064863204956</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.1512166209411443</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.0008960459381341934</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.01377156004309654</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>6.531365215778351e-05</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.002320984378457069</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.3512166209411443</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.0008544623851776123</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.3512166209411444</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.009296823292970657</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.1512166209411443</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.005874894559383392</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.01664409413933754</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.07024993002414703</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.0264732614159584</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.0045354925096035</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.9972187187152801</v>
+        <v>-0.16</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.0007979013025760651</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.9972187187152801</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.0006014052778482437</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.9972187187152801</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.0002306420356035233</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.9972187187152801</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.009617015719413757</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.9972187187152801</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.01027657836675644</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.7972187187152801</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.002547614276409149</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.7972187187152801</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.001681622117757797</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.7972187187152801</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.00105995312333107</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.7972187187152801</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.001527410000562668</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.7972187187152801</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.00623704120516777</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.7972187187152801</v>
+        <v>-0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.08553725481033325</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.7972187187152801</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.07930731773376465</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.7972187187152801</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.03423935547471046</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.7972187187152801</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.02929767966270447</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.7972187187152801</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001607944000447169</v>
+        <v>-0.0001655819800505415</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.853721954411314</v>
+        <v>1.908915605419707</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.02642953023314476</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.7972187187152801</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC40" t="n">
-        <v>3.710309428425272</v>
+        <v>3.820782201421234</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.2779738761016717</v>
+        <v>0.2862504102768729</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.02150680124759674</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.1512166209411443</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC41" t="n">
-        <v>2.410047276375039</v>
+        <v>2.481805283148065</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.3475577352364625</v>
+        <v>0.3579062094468367</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.009104777127504349</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.1512166209411443</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC42" t="n">
-        <v>2.827233128512782</v>
+        <v>2.911412704952789</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.49822252787801</v>
+        <v>0.5130568539070393</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.01447751745581627</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.1512166209411443</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>3.476316477828255</v>
+        <v>3.579822185635244</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.5329994170182389</v>
+        <v>0.5488688594293036</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.002680819481611252</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.1512166209411443</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>4.044129930562831</v>
+        <v>4.164541999836108</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5648719510311713</v>
+        <v>0.5816910990992846</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.005485419183969498</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.4947854768329915</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>4.640914747667312</v>
+        <v>4.779096175439199</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.2549162055742312</v>
+        <v>0.2625057084191442</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.005718972533941269</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>4.585405801437531</v>
+        <v>4.721934442921425</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1231128759542703</v>
+        <v>0.1267789021009197</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.09710638225078583</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>4.576515458634022</v>
+        <v>4.712779365589396</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.05865900719302262</v>
+        <v>0.06040575950735491</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.04073317348957062</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>4.570624055095799</v>
+        <v>4.706712529200177</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01738025465728496</v>
+        <v>0.01789816837695915</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.1074865609407425</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>4.54666257413703</v>
+        <v>4.682037535803007</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01149537223741126</v>
+        <v>0.01183757656008916</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.08773328363895416</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>4.552264760820843</v>
+        <v>4.687806569566344</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.005881019512496411</v>
+        <v>0.006056163523399848</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.06672576069831848</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>4.552524587959138</v>
+        <v>4.688074276883612</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.003005926453143595</v>
+        <v>0.003095519383377557</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.09604725241661072</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>4.552651919930332</v>
+        <v>4.68820554651627</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001126542951188564</v>
+        <v>0.001160602772461799</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.08326320350170135</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>4.551897555629047</v>
+        <v>4.687428883703615</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0006121044709894347</v>
+        <v>0.0006302546024891238</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.04216822981834412</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>4.551993833962312</v>
+        <v>4.687528140811389</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0002922290015088148</v>
+        <v>0.0003009710309649564</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.04070627689361572</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>4.551965797284904</v>
+        <v>4.687499426584645</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0001789996069603525</v>
+        <v>0.0001839193825475277</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.0250286590307951</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.2947854768329915</v>
+        <v>0.16</v>
       </c>
       <c r="JC56" t="n">
-        <v>4.552031428509947</v>
+        <v>4.687567135797627</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>9.073133164614701e-05</v>
+        <v>9.381943911860337e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.03630797937512398</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.2947854768329914</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>4.552034814656435</v>
+        <v>4.68757079099824</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>4.195737714690335e-05</v>
+        <v>4.295647027768853e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.0006655082106590271</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.2947854768329914</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>4.552026908132978</v>
+        <v>4.687562792321457</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>2.442036668854237e-05</v>
+        <v>2.569951306630508e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.008082382380962372</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.9407875746071271</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>4.552035050740018</v>
+        <v>4.687571494155336</v>
       </c>
     </row>
     <row r="60">
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.03821280598640442</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.9407875746071271</v>
+        <v>0.16</v>
       </c>
       <c r="JC60" t="n">
-        <v>4.552027305629676</v>
+        <v>4.687563635373489</v>
       </c>
     </row>
     <row r="61">
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.04002701491117477</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>4.552020661245013</v>
+        <v>4.687556854583018</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.06814301013946533</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>4.552016157342058</v>
+        <v>4.687552434039168</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.031182895915095e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.08718469738960266</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>4.552010724210589</v>
+        <v>4.687546855744045</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.1069525629281998</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>4.552005677589522</v>
+        <v>4.687541809122977</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.006847862154245377</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.4947854768329913</v>
+        <v>-0.16</v>
       </c>
       <c r="JC65" t="n">
-        <v>4.552005995869738</v>
+        <v>4.687542127403193</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.005755271762609482</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.2947854768329914</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>4.552007087116195</v>
+        <v>4.68754321864965</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.006505608558654785</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.2947854768329914</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>4.552006397509059</v>
+        <v>4.687542529042514</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.01063862442970276</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9407875746071271</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>4.552006427821461</v>
+        <v>4.687542559354916</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.107918381690979</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.9407875746071271</v>
+        <v>0.3</v>
       </c>
       <c r="JC69" t="n">
-        <v>4.552006238368951</v>
+        <v>4.687542369902406</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.06261445581912994</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.140787574607127</v>
+        <v>0.3</v>
       </c>
       <c r="JC70" t="n">
-        <v>4.552006291415654</v>
+        <v>4.687542422949109</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>9.253807365894318e-05</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.4947854768329915</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>4.552006344462357</v>
+        <v>4.687542475995811</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.00234617292881012</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.2947854768329913</v>
+        <v>-0.16</v>
       </c>
       <c r="JC72" t="n">
-        <v>4.552006306571855</v>
+        <v>4.687542438105309</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.02774370834231377</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.2947854768329913</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>4.552006177744147</v>
+        <v>4.687542309277602</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.02684234827756882</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.9407875746071271</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>4.55200603376024</v>
+        <v>4.687542165293696</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.0164839755743742</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.2947854768329914</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>4.552005874620132</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.004630081355571747</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.3512166209411444</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>4.552005927666834</v>
+        <v>4.68754205920029</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.03809492662549019</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.3512166209411444</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>4.552005874620132</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.02094819582998753</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.2947854768329914</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>4.552005874620132</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.0601031482219696</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9407875746071271</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC79" t="n">
-        <v>4.552005692745722</v>
+        <v>4.687541824279178</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.05025205016136169</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.4947854768329913</v>
+        <v>-0.3</v>
       </c>
       <c r="JC80" t="n">
-        <v>4.552005859463931</v>
+        <v>4.687541990997386</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.007495388388633728</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.1512166209411444</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>4.552006056494541</v>
+        <v>4.687542188027996</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.02666735276579857</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.3512166209411445</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>4.552005897354434</v>
+        <v>4.687542028887888</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.0496465191245079</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.2947854768329913</v>
+        <v>-0.3</v>
       </c>
       <c r="JC83" t="n">
-        <v>4.552005935244934</v>
+        <v>4.68754206677839</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.07310494035482407</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.3</v>
       </c>
       <c r="JC84" t="n">
-        <v>4.552006132275545</v>
+        <v>4.687542263809</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.009603265672922134</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.4947854768329913</v>
+        <v>-0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>4.552006109541244</v>
+        <v>4.687542241074699</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.0330817811191082</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.1512166209411444</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>4.552005957979236</v>
+        <v>4.687542089512691</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.01577423885464668</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.3512166209411445</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>4.552005882198232</v>
+        <v>4.687542013731687</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.01887982897460461</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.2947854768329913</v>
+        <v>0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>4.552005980713538</v>
+        <v>4.687542112246993</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.06669227778911591</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.140787574607127</v>
+        <v>0.16</v>
       </c>
       <c r="JC89" t="n">
-        <v>4.552005988291638</v>
+        <v>4.687542119825094</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.03407534211874008</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>4.552006253525152</v>
+        <v>4.687542385058607</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.01101171970367432</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>4.552005957979236</v>
+        <v>4.687542089512691</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.04375734180212021</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>4.552006200478449</v>
+        <v>4.687542332011904</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.03261633962392807</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.4947854768329915</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>4.552006283837553</v>
+        <v>4.687542415371008</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.02910155057907104</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.4947854768329913</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>4.552006117119345</v>
+        <v>4.6875422486528</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.07825706899166107</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.2947854768329913</v>
+        <v>-0.3</v>
       </c>
       <c r="JC95" t="n">
-        <v>4.552006306571855</v>
+        <v>4.687542438105309</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.01783505082130432</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.2947854768329913</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>4.552005957979236</v>
+        <v>4.687542089512691</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.05304277315735817</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.3512166209411445</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>4.552005753370525</v>
+        <v>4.687541884903981</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.02933645620942116</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.3512166209411445</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>4.552005867042031</v>
+        <v>4.687541998575486</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.01622727885842323</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.3512166209411445</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>4.552005882198232</v>
+        <v>4.687542013731687</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.01620214432477951</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.3512166209411445</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>4.55200564727712</v>
+        <v>4.687541778810576</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.05231865867972374</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>4.552005707901923</v>
+        <v>4.687541839435378</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.02611289545893669</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.3512166209411445</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>4.552005579074216</v>
+        <v>4.687541710607671</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.05630844086408615</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.3512166209411445</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>4.552005715480024</v>
+        <v>4.687541847013479</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.03425296023488045</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.3512166209411445</v>
+        <v>-0.16</v>
       </c>
       <c r="JC104" t="n">
-        <v>4.552005889776332</v>
+        <v>4.687542021309787</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.02341774851083755</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.1512166209411445</v>
+        <v>-0.16</v>
       </c>
       <c r="JC105" t="n">
-        <v>4.55200603376024</v>
+        <v>4.687542165293696</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.0008876286447048187</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.1512166209411444</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>4.552005867042031</v>
+        <v>4.687541998575486</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.003675889223814011</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.1512166209411444</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>4.552005859463931</v>
+        <v>4.687541990997386</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.06502224504947662</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>4.552005571496116</v>
+        <v>4.687541703029571</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.0454382635653019</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>4.552005586652317</v>
+        <v>4.687541718185773</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.03191206231713295</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>4.552005813995328</v>
+        <v>4.687541945528784</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.02057768777012825</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>4.552005798839128</v>
+        <v>4.687541930372583</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.0535961426794529</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>4.552005904932534</v>
+        <v>4.687542036465988</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.04522579535841942</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>4.552005632120919</v>
+        <v>4.687541763654375</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.0366581566631794</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>4.552005730636224</v>
+        <v>4.687541862169679</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.03526033088564873</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.9972187187152801</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC115" t="n">
-        <v>4.552005882198232</v>
+        <v>4.687542013731687</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.03646119311451912</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.9972187187152801</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC116" t="n">
-        <v>4.552005897354434</v>
+        <v>4.687542028887888</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.02426199615001678</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7972187187152801</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>4.552005874620132</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.02108307555317879</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7972187187152801</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>4.552005957979236</v>
+        <v>4.687542089512691</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.05197649821639061</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7972187187152801</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>4.552006056494541</v>
+        <v>4.687542188027996</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.04241703078150749</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7972187187152801</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>4.552005889776332</v>
+        <v>4.687542021309787</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.03912180289626122</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.7972187187152801</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>4.552005874620132</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.03264253214001656</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.7972187187152801</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>4.55200584430773</v>
+        <v>4.687541975841185</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.0395081453025341</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.7972187187152801</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>4.55200582915153</v>
+        <v>4.687541960684985</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.0391971655189991</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.7972187187152801</v>
+        <v>-0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>4.552005867042031</v>
+        <v>4.687541998575486</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.01288145035505295</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.7972187187152801</v>
+        <v>-0.4400000000000004</v>
       </c>
       <c r="JC125" t="n">
-        <v>4.552005882198232</v>
+        <v>4.687542013731687</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.0315866507589817</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.7972187187152801</v>
+        <v>-0.7200000000000004</v>
       </c>
       <c r="JC126" t="n">
-        <v>4.552005874620132</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_4_000007.xlsx
+++ b/out/Attention-mamba2_repeat_4_000007.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.07961051166057587</v>
+        <v>-0.07839041948318481</v>
       </c>
       <c r="JB2" t="n">
         <v>-1.28</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.04634322226047516</v>
+        <v>-0.04490533471107483</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.8599999999999997</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.02621113881468773</v>
+        <v>-0.02497452311217785</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.4399999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.04897912219166756</v>
+        <v>0.04830750077962875</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.16</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.01812337711453438</v>
+        <v>0.01799620315432549</v>
       </c>
       <c r="JB6" t="n">
         <v>0.5799999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.003646623343229294</v>
+        <v>0.003721263259649277</v>
       </c>
       <c r="JB7" t="n">
         <v>0.8599999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.004249747842550278</v>
+        <v>-0.00405840203166008</v>
       </c>
       <c r="JB8" t="n">
         <v>0.7199999999999999</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.003217112272977829</v>
+        <v>0.003600016236305237</v>
       </c>
       <c r="JB9" t="n">
         <v>0.5799999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.0004043895751237869</v>
+        <v>-0.0001134313642978668</v>
       </c>
       <c r="JB10" t="n">
         <v>0.4399999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.002018257975578308</v>
+        <v>0.00236152857542038</v>
       </c>
       <c r="JB11" t="n">
         <v>0.5799999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.0004030074924230576</v>
+        <v>-0.0001041591167449951</v>
       </c>
       <c r="JB12" t="n">
         <v>0.4399999999999999</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.0008475035429000854</v>
+        <v>-0.0005304403603076935</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.02000000000000007</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.002036064863204956</v>
+        <v>0.002417270094156265</v>
       </c>
       <c r="JB14" t="n">
         <v>0.1199999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.0008960459381341934</v>
+        <v>0.001202339306473732</v>
       </c>
       <c r="JB15" t="n">
         <v>0.8599999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.01377156004309654</v>
+        <v>0.0141887329518795</v>
       </c>
       <c r="JB16" t="n">
         <v>0.8599999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>6.531365215778351e-05</v>
+        <v>0.0002813227474689484</v>
       </c>
       <c r="JB17" t="n">
         <v>0.8599999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.002320984378457069</v>
+        <v>0.002633139491081238</v>
       </c>
       <c r="JB18" t="n">
         <v>0.8599999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.0008544623851776123</v>
+        <v>-0.0005886107683181763</v>
       </c>
       <c r="JB19" t="n">
         <v>0.7199999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.009296823292970657</v>
+        <v>0.009689942002296448</v>
       </c>
       <c r="JB20" t="n">
         <v>0.7199999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.005874894559383392</v>
+        <v>0.006188668310642242</v>
       </c>
       <c r="JB21" t="n">
         <v>0.1199999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.01664409413933754</v>
+        <v>0.01708376035094261</v>
       </c>
       <c r="JB22" t="n">
         <v>0.2599999999999998</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.07024993002414703</v>
+        <v>0.07059960812330246</v>
       </c>
       <c r="JB23" t="n">
         <v>0.1199999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.0264732614159584</v>
+        <v>0.02656592428684235</v>
       </c>
       <c r="JB24" t="n">
         <v>0.1199999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.0045354925096035</v>
+        <v>0.004709493368864059</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.16</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.0007979013025760651</v>
+        <v>0.001063933596014977</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.4399999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.0006014052778482437</v>
+        <v>0.0009106770157814026</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.5799999999999998</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.0002306420356035233</v>
+        <v>0.0005243066698312759</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.4399999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.009617015719413757</v>
+        <v>0.009993862360715866</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.4399999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.01027657836675644</v>
+        <v>0.01055135950446129</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.4399999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.002547614276409149</v>
+        <v>0.002796605229377747</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.4399999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.001681622117757797</v>
+        <v>0.001993238925933838</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.5799999999999998</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.00105995312333107</v>
+        <v>0.001431901007890701</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.7199999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.001527410000562668</v>
+        <v>0.001869186758995056</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.5799999999999998</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.00623704120516777</v>
+        <v>0.006508029997348785</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.3</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.08553725481033325</v>
+        <v>0.08531463891267776</v>
       </c>
       <c r="JB36" t="n">
         <v>0.5799999999999998</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.07930731773376465</v>
+        <v>0.07786089926958084</v>
       </c>
       <c r="JB37" t="n">
         <v>0.8599999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.03423935547471046</v>
+        <v>0.03308029472827911</v>
       </c>
       <c r="JB38" t="n">
         <v>0.9999999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.02929767966270447</v>
+        <v>0.02806425839662552</v>
       </c>
       <c r="JB39" t="n">
         <v>0.8599999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.02642953023314476</v>
+        <v>0.02509937062859535</v>
       </c>
       <c r="JB40" t="n">
         <v>0.5799999999999998</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.02150680124759674</v>
+        <v>0.02011312544345856</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC41" t="n">
         <v>2.481805283148065</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.009104777127504349</v>
+        <v>-0.006452571600675583</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>2.911412704952789</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.01447751745581627</v>
+        <v>0.01302474737167358</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>3.579822185635244</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.002680819481611252</v>
+        <v>0.001287706196308136</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>4.164541999836108</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.005485419183969498</v>
+        <v>-0.006733879446983337</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
         <v>4.779096175439199</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.005718972533941269</v>
+        <v>-0.006849832832813263</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.09710638225078583</v>
+        <v>-0.102977342903614</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.9999999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.04073317348957062</v>
+        <v>-0.04169116169214249</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.1074865609407425</v>
+        <v>-0.1130961403250694</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.08773328363895416</v>
+        <v>-0.09237036854028702</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.06672576069831848</v>
+        <v>-0.07084310054779053</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.09604725241661072</v>
+        <v>-0.1009333804249763</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.08326320350170135</v>
+        <v>-0.08803875744342804</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.04216822981834412</v>
+        <v>-0.04585324972867966</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.04070627689361572</v>
+        <v>-0.04375219345092773</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.1199999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.0250286590307951</v>
+        <v>-0.02745411172509193</v>
       </c>
       <c r="JB56" t="n">
         <v>0.16</v>
@@ -46256,10 +46256,10 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.03630797937512398</v>
+        <v>0.03450793772935867</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC57" t="n">
         <v>4.68757079099824</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.0006655082106590271</v>
+        <v>-0.001195980235934258</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
         <v>4.687562792321457</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.008082382380962372</v>
+        <v>-0.02140898443758488</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="JC59" t="n">
         <v>4.687571494155336</v>
@@ -48641,10 +48641,10 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.03821280598640442</v>
+        <v>-0.04237660020589828</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.16</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC60" t="n">
         <v>4.687563635373489</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.04002701491117477</v>
+        <v>-0.04317189007997513</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
         <v>4.687556854583018</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.06814301013946533</v>
+        <v>-0.07245764136314392</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.08718469738960266</v>
+        <v>-0.09217789024114609</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.7199999999999999</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.1069525629281998</v>
+        <v>-0.1122712194919586</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.4399999999999999</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.006847862154245377</v>
+        <v>-0.008357217535376549</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.16</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
         <v>4.687542127403193</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.005755271762609482</v>
+        <v>-0.0002719387412071228</v>
       </c>
       <c r="JB66" t="n">
         <v>0.7199999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.006505608558654785</v>
+        <v>-0.01040939055383205</v>
       </c>
       <c r="JB67" t="n">
         <v>0.7199999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.01063862442970276</v>
+        <v>-0.0171162374317646</v>
       </c>
       <c r="JB68" t="n">
         <v>0.4399999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.107918381690979</v>
+        <v>-0.1131118312478065</v>
       </c>
       <c r="JB69" t="n">
         <v>0.3</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.06261445581912994</v>
+        <v>-0.0666966512799263</v>
       </c>
       <c r="JB70" t="n">
         <v>0.3</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>9.253807365894318e-05</v>
+        <v>-0.002425670623779297</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.4399999999999999</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.00234617292881012</v>
+        <v>0.0002022981643676758</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.16</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.02774370834231377</v>
+        <v>-0.03041850589215755</v>
       </c>
       <c r="JB73" t="n">
         <v>0.1199999999999999</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.02684234827756882</v>
+        <v>-0.02967151626944542</v>
       </c>
       <c r="JB74" t="n">
         <v>0.8599999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.0164839755743742</v>
+        <v>-0.01907063089311123</v>
       </c>
       <c r="JB75" t="n">
         <v>0.8599999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.004630081355571747</v>
+        <v>0.002722792327404022</v>
       </c>
       <c r="JB76" t="n">
         <v>0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.03809492662549019</v>
+        <v>0.03698258101940155</v>
       </c>
       <c r="JB77" t="n">
         <v>0.7199999999999999</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.02094819582998753</v>
+        <v>-0.02325136587023735</v>
       </c>
       <c r="JB78" t="n">
         <v>0.4399999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.0601031482219696</v>
+        <v>-0.06375880539417267</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.1600000000000001</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.05025205016136169</v>
+        <v>-0.05410738661885262</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.3</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.007495388388633728</v>
+        <v>0.005333445966243744</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.5799999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.02666735276579857</v>
+        <v>0.02529903501272202</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.5799999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.0496465191245079</v>
+        <v>-0.05284903943538666</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.3</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.07310494035482407</v>
+        <v>-0.07744116336107254</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.3</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.009603265672922134</v>
+        <v>-0.0123516246676445</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.3</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.0330817811191082</v>
+        <v>0.03163277357816696</v>
       </c>
       <c r="JB86" t="n">
         <v>0.5799999999999998</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.01577423885464668</v>
+        <v>0.01437290757894516</v>
       </c>
       <c r="JB87" t="n">
         <v>0.5799999999999998</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.01887982897460461</v>
+        <v>-0.02127611637115479</v>
       </c>
       <c r="JB88" t="n">
         <v>0.3</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.06669227778911591</v>
+        <v>-0.07086525112390518</v>
       </c>
       <c r="JB89" t="n">
         <v>0.16</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.03407534211874008</v>
+        <v>-0.03745907917618752</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.5799999999999998</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.01101171970367432</v>
+        <v>-0.01353875547647476</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.8599999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.04375734180212021</v>
+        <v>-0.04697814583778381</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.5799999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.03261633962392807</v>
+        <v>-0.03593791276216507</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.5799999999999998</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.02910155057907104</v>
+        <v>0.02845767885446548</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.5799999999999998</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.07825706899166107</v>
+        <v>-0.08313818275928497</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.3</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.01783505082130432</v>
+        <v>-0.02077913470566273</v>
       </c>
       <c r="JB96" t="n">
         <v>0.5799999999999998</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.05304277315735817</v>
+        <v>0.05201669782400131</v>
       </c>
       <c r="JB97" t="n">
         <v>0.4399999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.02933645620942116</v>
+        <v>0.02837425470352173</v>
       </c>
       <c r="JB98" t="n">
         <v>0.7199999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.01622727885842323</v>
+        <v>-0.01833299361169338</v>
       </c>
       <c r="JB99" t="n">
         <v>0.8599999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.01620214432477951</v>
+        <v>0.01460070908069611</v>
       </c>
       <c r="JB100" t="n">
         <v>0.7199999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.05231865867972374</v>
+        <v>0.05190594494342804</v>
       </c>
       <c r="JB101" t="n">
         <v>0.4399999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.02611289545893669</v>
+        <v>0.02536853775382042</v>
       </c>
       <c r="JB102" t="n">
         <v>0.5799999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.05630844086408615</v>
+        <v>-0.05951879546046257</v>
       </c>
       <c r="JB103" t="n">
         <v>0.5799999999999998</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.03425296023488045</v>
+        <v>0.03248199447989464</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.16</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.02341774851083755</v>
+        <v>0.02216310799121857</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.16</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.0008876286447048187</v>
+        <v>-0.0009576268494129181</v>
       </c>
       <c r="JB106" t="n">
         <v>0.1199999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.003675889223814011</v>
+        <v>0.002022625878453255</v>
       </c>
       <c r="JB107" t="n">
         <v>0.7199999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.06502224504947662</v>
+        <v>0.06489585340023041</v>
       </c>
       <c r="JB108" t="n">
         <v>0.7199999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.0454382635653019</v>
+        <v>0.04559112340211868</v>
       </c>
       <c r="JB109" t="n">
         <v>0.8599999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.03191206231713295</v>
+        <v>0.03158899024128914</v>
       </c>
       <c r="JB110" t="n">
         <v>0.9999999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.02057768777012825</v>
+        <v>0.01980194076895714</v>
       </c>
       <c r="JB111" t="n">
         <v>0.8599999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.0535961426794529</v>
+        <v>0.05342473834753036</v>
       </c>
       <c r="JB112" t="n">
         <v>0.7199999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.04522579535841942</v>
+        <v>0.04539065808057785</v>
       </c>
       <c r="JB113" t="n">
         <v>0.7199999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.0366581566631794</v>
+        <v>0.03656696528196335</v>
       </c>
       <c r="JB114" t="n">
         <v>0.1199999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.03526033088564873</v>
+        <v>0.03496213257312775</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.02000000000000007</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.03646119311451912</v>
+        <v>0.03609894216060638</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.02000000000000007</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.02426199615001678</v>
+        <v>0.02345161139965057</v>
       </c>
       <c r="JB117" t="n">
         <v>0.1199999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.02108307555317879</v>
+        <v>0.02016421407461166</v>
       </c>
       <c r="JB118" t="n">
         <v>0.1199999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.05197649821639061</v>
+        <v>0.05172498524188995</v>
       </c>
       <c r="JB119" t="n">
         <v>0.1199999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.04241703078150749</v>
+        <v>0.04237354546785355</v>
       </c>
       <c r="JB120" t="n">
         <v>0.8599999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.03912180289626122</v>
+        <v>0.03896372020244598</v>
       </c>
       <c r="JB121" t="n">
         <v>0.9999999999999998</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.03264253214001656</v>
+        <v>0.03224853426218033</v>
       </c>
       <c r="JB122" t="n">
         <v>0.8599999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.0395081453025341</v>
+        <v>0.03918637335300446</v>
       </c>
       <c r="JB123" t="n">
         <v>0.5799999999999998</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.0391971655189991</v>
+        <v>0.03890613466501236</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.16</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.01288145035505295</v>
+        <v>0.01161527261137962</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.4400000000000004</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.0315866507589817</v>
+        <v>0.02869847044348717</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.7200000000000004</v>
